--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -558,9 +558,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>நந்தகுமார் லட்சுமணன்</v>
+      </c>
+      <c r="C15">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -569,9 +569,20 @@
         <v>300</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>கண்ணன் Post</v>
+      </c>
+      <c r="C16">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -580,9 +580,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>நாகவேல்</v>
+      </c>
+      <c r="C17">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -591,9 +591,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>தியாகராஜன் சலூன்</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -602,9 +602,20 @@
         <v>100</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>அரவிந்த் அன்பானந்தன்</v>
+      </c>
+      <c r="C19">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -613,9 +613,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>சூர்யா கார்த்திக்</v>
+      </c>
+      <c r="C20">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -624,9 +624,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SRS நண்பர்கள்</v>
+      </c>
+      <c r="C21">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -635,9 +635,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>விஜயலட்சுமி லட்சுமணன்</v>
+      </c>
+      <c r="C22">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
   </ignoredErrors>
 </worksheet>
 </file>